--- a/5_checking_accuracy/ground_true.xlsx
+++ b/5_checking_accuracy/ground_true.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cynthiasyz/Desktop/Fall 2025/NLP/final/F25_NLP_Cross-Domain-Job-Matching/5_checking_accuracy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76AC5BDD-1DF2-2D45-BE55-73AE2B50242A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0173D2-6A54-B444-83C5-AE9C490BCD53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="940" windowWidth="34200" windowHeight="20000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="800" windowWidth="34200" windowHeight="20000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="84">
   <si>
     <t>resume_id</t>
   </si>
@@ -113,12 +113,6 @@
   </si>
   <si>
     <t>Customer Service Representative</t>
-  </si>
-  <si>
-    <t>Senior Quality Engineer</t>
-  </si>
-  <si>
-    <t>Jacksonville, FL</t>
   </si>
   <si>
     <t>Staff Accountant</t>
@@ -648,10 +642,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="5" width="15" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -667,20 +664,8 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -696,20 +681,8 @@
       <c r="E2">
         <v>0.96</v>
       </c>
-      <c r="F2">
-        <v>103</v>
-      </c>
-      <c r="G2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -726,7 +699,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -743,7 +716,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
@@ -760,7 +733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -776,20 +749,8 @@
       <c r="E6">
         <v>1</v>
       </c>
-      <c r="F6">
-        <v>1018</v>
-      </c>
-      <c r="G6" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" t="s">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
@@ -806,7 +767,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6</v>
       </c>
@@ -823,7 +784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>7</v>
       </c>
@@ -831,16 +792,16 @@
         <v>617</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E9">
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>8</v>
       </c>
@@ -857,7 +818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>9</v>
       </c>
@@ -874,7 +835,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
@@ -882,16 +843,16 @@
         <v>231</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E12">
         <v>0.8</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>11</v>
       </c>
@@ -908,7 +869,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>12</v>
       </c>
@@ -925,7 +886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>13</v>
       </c>
@@ -942,7 +903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1052,10 +1013,10 @@
         <v>65</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D22" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E22">
         <v>0.65255147218704224</v>
@@ -1086,10 +1047,10 @@
         <v>913</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E24">
         <v>0.78</v>
@@ -1120,10 +1081,10 @@
         <v>325</v>
       </c>
       <c r="C26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E26">
         <v>0.8</v>
@@ -1171,7 +1132,7 @@
         <v>1033</v>
       </c>
       <c r="C29" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D29" t="s">
         <v>8</v>
@@ -1188,10 +1149,10 @@
         <v>391</v>
       </c>
       <c r="C30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E30">
         <v>0.6</v>
@@ -1222,10 +1183,10 @@
         <v>885</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E32" s="2">
         <v>0.62</v>
@@ -1256,10 +1217,10 @@
         <v>890</v>
       </c>
       <c r="C34" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D34" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E34">
         <v>0.7</v>
@@ -1273,10 +1234,10 @@
         <v>213</v>
       </c>
       <c r="C35" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E35">
         <v>0.8</v>
@@ -1307,10 +1268,10 @@
         <v>617</v>
       </c>
       <c r="C37" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D37" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E37">
         <v>0.82</v>
@@ -1341,7 +1302,7 @@
         <v>211</v>
       </c>
       <c r="C39" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D39" t="s">
         <v>6</v>
@@ -1358,7 +1319,7 @@
         <v>133</v>
       </c>
       <c r="C40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D40" t="s">
         <v>13</v>
@@ -1375,10 +1336,10 @@
         <v>944</v>
       </c>
       <c r="C41" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -1392,10 +1353,10 @@
         <v>213</v>
       </c>
       <c r="C42" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D42" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E42">
         <v>0.8</v>
@@ -1412,7 +1373,7 @@
         <v>24</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E43" s="2">
         <v>0.67</v>
@@ -1426,10 +1387,10 @@
         <v>7</v>
       </c>
       <c r="C44" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D44" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E44">
         <v>0.8</v>
@@ -1443,10 +1404,10 @@
         <v>1177</v>
       </c>
       <c r="C45" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D45" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E45">
         <v>0.92</v>
@@ -1477,7 +1438,7 @@
         <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D47" t="s">
         <v>19</v>
@@ -1494,10 +1455,10 @@
         <v>412</v>
       </c>
       <c r="C48" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D48" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E48">
         <v>0.75</v>
@@ -1528,10 +1489,10 @@
         <v>68</v>
       </c>
       <c r="C50" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D50" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E50">
         <v>0.9</v>
@@ -1562,10 +1523,10 @@
         <v>213</v>
       </c>
       <c r="C52" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D52" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E52">
         <v>0.8</v>
@@ -1596,10 +1557,10 @@
         <v>68</v>
       </c>
       <c r="C54" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D54" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E54">
         <v>0.75</v>
@@ -1613,10 +1574,10 @@
         <v>968</v>
       </c>
       <c r="C55" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D55" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E55">
         <v>0.7</v>
@@ -1630,7 +1591,7 @@
         <v>738</v>
       </c>
       <c r="C56" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D56" t="s">
         <v>19</v>
@@ -1647,7 +1608,7 @@
         <v>994</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>8</v>
@@ -1664,10 +1625,10 @@
         <v>474</v>
       </c>
       <c r="C58" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D58" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E58">
         <v>0.92</v>
@@ -1698,7 +1659,7 @@
         <v>1041</v>
       </c>
       <c r="C60" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D60" t="s">
         <v>8</v>
@@ -1715,10 +1676,10 @@
         <v>427</v>
       </c>
       <c r="C61" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D61" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E61">
         <v>0.8</v>
@@ -1732,7 +1693,7 @@
         <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D62" t="s">
         <v>19</v>
@@ -1749,10 +1710,10 @@
         <v>213</v>
       </c>
       <c r="C63" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D63" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E63">
         <v>0.98</v>
@@ -1800,10 +1761,10 @@
         <v>391</v>
       </c>
       <c r="C66" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D66" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E66">
         <v>0.54029422998428345</v>
@@ -1851,10 +1812,10 @@
         <v>895</v>
       </c>
       <c r="C69" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D69" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E69">
         <v>1</v>
@@ -1902,10 +1863,10 @@
         <v>712</v>
       </c>
       <c r="C72" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D72" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E72">
         <v>0.85</v>
@@ -1936,10 +1897,10 @@
         <v>470</v>
       </c>
       <c r="C74" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D74" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E74">
         <v>1</v>
@@ -1953,10 +1914,10 @@
         <v>213</v>
       </c>
       <c r="C75" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D75" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E75">
         <v>0.9</v>
@@ -1970,10 +1931,10 @@
         <v>895</v>
       </c>
       <c r="C76" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D76" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E76">
         <v>0.75</v>
@@ -1987,7 +1948,7 @@
         <v>671</v>
       </c>
       <c r="C77" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D77" t="s">
         <v>6</v>
@@ -2004,7 +1965,7 @@
         <v>1034</v>
       </c>
       <c r="C78" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D78" t="s">
         <v>8</v>
@@ -2021,7 +1982,7 @@
         <v>13</v>
       </c>
       <c r="C79" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D79" t="s">
         <v>19</v>
@@ -2038,10 +1999,10 @@
         <v>325</v>
       </c>
       <c r="C80" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D80" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E80">
         <v>0.45585787296295172</v>
@@ -2072,10 +2033,10 @@
         <v>391</v>
       </c>
       <c r="C82" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D82" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E82">
         <v>0.64289402961730957</v>
@@ -2089,10 +2050,10 @@
         <v>740</v>
       </c>
       <c r="C83" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D83" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E83">
         <v>0.62479013204574585</v>
@@ -2106,10 +2067,10 @@
         <v>325</v>
       </c>
       <c r="C84" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D84" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E84">
         <v>0.54179960489273071</v>
@@ -2123,10 +2084,10 @@
         <v>213</v>
       </c>
       <c r="C85" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D85" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E85">
         <v>0.62921535968780518</v>
@@ -2140,10 +2101,10 @@
         <v>231</v>
       </c>
       <c r="C86" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D86" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E86">
         <v>0.60121119022369385</v>
@@ -2157,7 +2118,7 @@
         <v>50</v>
       </c>
       <c r="C87" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D87" t="s">
         <v>8</v>
@@ -2174,7 +2135,7 @@
         <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D88" t="s">
         <v>19</v>
@@ -2191,10 +2152,10 @@
         <v>231</v>
       </c>
       <c r="C89" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D89" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E89">
         <v>0.60121119022369385</v>
@@ -2225,10 +2186,10 @@
         <v>444</v>
       </c>
       <c r="C91" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D91" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E91">
         <v>0.59985661506652832</v>
@@ -2242,10 +2203,10 @@
         <v>391</v>
       </c>
       <c r="C92" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D92" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E92">
         <v>0.56909620761871338</v>
@@ -2259,7 +2220,7 @@
         <v>992</v>
       </c>
       <c r="C93" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D93" t="s">
         <v>8</v>
@@ -2327,7 +2288,7 @@
         <v>50</v>
       </c>
       <c r="C97" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D97" t="s">
         <v>8</v>
@@ -2344,10 +2305,10 @@
         <v>391</v>
       </c>
       <c r="C98" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D98" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E98">
         <v>0.60087299346923828</v>
@@ -2361,10 +2322,10 @@
         <v>12</v>
       </c>
       <c r="C99" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D99" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E99">
         <v>0.59785550832748413</v>
@@ -2378,7 +2339,7 @@
         <v>1018</v>
       </c>
       <c r="C100" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D100" t="s">
         <v>8</v>
@@ -2395,10 +2356,10 @@
         <v>12</v>
       </c>
       <c r="C101" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D101" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E101">
         <v>0.56807112693786621</v>

--- a/5_checking_accuracy/ground_true.xlsx
+++ b/5_checking_accuracy/ground_true.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cynthiasyz/Desktop/Fall 2025/NLP/final/F25_NLP_Cross-Domain-Job-Matching/5_checking_accuracy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0173D2-6A54-B444-83C5-AE9C490BCD53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E3E157-1CB2-3848-A408-261A225AA5A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="800" windowWidth="34200" windowHeight="20000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,18 +25,6 @@
     <t>resume_id</t>
   </si>
   <si>
-    <t>top1_job_id</t>
-  </si>
-  <si>
-    <t>top1_job_title</t>
-  </si>
-  <si>
-    <t>top1_job_location</t>
-  </si>
-  <si>
-    <t>top1_score</t>
-  </si>
-  <si>
     <t>Project Manager</t>
   </si>
   <si>
@@ -272,6 +260,18 @@
   </si>
   <si>
     <t>Eden Prairie, MN</t>
+  </si>
+  <si>
+    <t>match_job_title</t>
+  </si>
+  <si>
+    <t>match_job_id</t>
+  </si>
+  <si>
+    <t>match_job_location</t>
+  </si>
+  <si>
+    <t>match_score</t>
   </si>
 </sst>
 </file>
@@ -653,16 +653,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -673,10 +673,10 @@
         <v>1224</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>0.96</v>
@@ -690,10 +690,10 @@
         <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E3">
         <v>0.9</v>
@@ -707,10 +707,10 @@
         <v>85</v>
       </c>
       <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
         <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
       </c>
       <c r="E4">
         <v>0.78</v>
@@ -724,10 +724,10 @@
         <v>1011</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -741,10 +741,10 @@
         <v>1209</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -758,10 +758,10 @@
         <v>131</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E7">
         <v>0.7</v>
@@ -775,10 +775,10 @@
         <v>960</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -792,10 +792,10 @@
         <v>617</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E9">
         <v>0.8</v>
@@ -809,10 +809,10 @@
         <v>964</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -826,10 +826,10 @@
         <v>172</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E11">
         <v>0.85</v>
@@ -843,10 +843,10 @@
         <v>231</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E12">
         <v>0.8</v>
@@ -860,10 +860,10 @@
         <v>1159</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E13">
         <v>0.875</v>
@@ -877,10 +877,10 @@
         <v>304</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -894,10 +894,10 @@
         <v>960</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -911,10 +911,10 @@
         <v>240</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -928,10 +928,10 @@
         <v>811</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E17">
         <v>0.92</v>
@@ -945,10 +945,10 @@
         <v>1013</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E18">
         <v>0.8</v>
@@ -962,10 +962,10 @@
         <v>228</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E19">
         <v>0.7</v>
@@ -979,10 +979,10 @@
         <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D20" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E20">
         <v>0.75</v>
@@ -996,10 +996,10 @@
         <v>1016</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -1013,10 +1013,10 @@
         <v>65</v>
       </c>
       <c r="C22" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E22">
         <v>0.65255147218704224</v>
@@ -1030,10 +1030,10 @@
         <v>811</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E23">
         <v>0.97</v>
@@ -1047,10 +1047,10 @@
         <v>913</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E24">
         <v>0.78</v>
@@ -1064,10 +1064,10 @@
         <v>960</v>
       </c>
       <c r="C25" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E25">
         <v>0.85</v>
@@ -1081,10 +1081,10 @@
         <v>325</v>
       </c>
       <c r="C26" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E26">
         <v>0.8</v>
@@ -1098,10 +1098,10 @@
         <v>1209</v>
       </c>
       <c r="C27" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E27">
         <v>0.85</v>
@@ -1115,10 +1115,10 @@
         <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D28" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E28">
         <v>0.9</v>
@@ -1132,10 +1132,10 @@
         <v>1033</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D29" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E29">
         <v>0.96285714285714286</v>
@@ -1149,10 +1149,10 @@
         <v>391</v>
       </c>
       <c r="C30" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D30" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E30">
         <v>0.6</v>
@@ -1166,10 +1166,10 @@
         <v>240</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E31">
         <v>0.96</v>
@@ -1183,10 +1183,10 @@
         <v>885</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E32" s="2">
         <v>0.62</v>
@@ -1200,10 +1200,10 @@
         <v>964</v>
       </c>
       <c r="C33" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E33">
         <v>0.85</v>
@@ -1217,10 +1217,10 @@
         <v>890</v>
       </c>
       <c r="C34" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D34" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E34">
         <v>0.7</v>
@@ -1234,10 +1234,10 @@
         <v>213</v>
       </c>
       <c r="C35" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D35" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E35">
         <v>0.8</v>
@@ -1251,10 +1251,10 @@
         <v>960</v>
       </c>
       <c r="C36" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -1268,10 +1268,10 @@
         <v>617</v>
       </c>
       <c r="C37" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D37" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E37">
         <v>0.82</v>
@@ -1285,10 +1285,10 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D38" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -1302,10 +1302,10 @@
         <v>211</v>
       </c>
       <c r="C39" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D39" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E39">
         <v>0.75</v>
@@ -1319,10 +1319,10 @@
         <v>133</v>
       </c>
       <c r="C40" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D40" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E40">
         <v>0.85</v>
@@ -1336,10 +1336,10 @@
         <v>944</v>
       </c>
       <c r="C41" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -1353,10 +1353,10 @@
         <v>213</v>
       </c>
       <c r="C42" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D42" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E42">
         <v>0.8</v>
@@ -1370,10 +1370,10 @@
         <v>388</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E43" s="2">
         <v>0.67</v>
@@ -1387,10 +1387,10 @@
         <v>7</v>
       </c>
       <c r="C44" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D44" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E44">
         <v>0.8</v>
@@ -1404,10 +1404,10 @@
         <v>1177</v>
       </c>
       <c r="C45" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E45">
         <v>0.92</v>
@@ -1421,10 +1421,10 @@
         <v>240</v>
       </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D46" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E46">
         <v>0.8</v>
@@ -1438,10 +1438,10 @@
         <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D47" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E47">
         <v>0.62608224153518677</v>
@@ -1455,10 +1455,10 @@
         <v>412</v>
       </c>
       <c r="C48" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D48" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E48">
         <v>0.75</v>
@@ -1472,10 +1472,10 @@
         <v>960</v>
       </c>
       <c r="C49" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E49">
         <v>0.78</v>
@@ -1489,10 +1489,10 @@
         <v>68</v>
       </c>
       <c r="C50" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D50" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E50">
         <v>0.9</v>
@@ -1506,10 +1506,10 @@
         <v>811</v>
       </c>
       <c r="C51" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D51" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E51">
         <v>0.75</v>
@@ -1523,10 +1523,10 @@
         <v>213</v>
       </c>
       <c r="C52" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D52" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E52">
         <v>0.8</v>
@@ -1540,10 +1540,10 @@
         <v>0</v>
       </c>
       <c r="C53" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -1557,10 +1557,10 @@
         <v>68</v>
       </c>
       <c r="C54" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D54" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E54">
         <v>0.75</v>
@@ -1574,10 +1574,10 @@
         <v>968</v>
       </c>
       <c r="C55" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D55" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E55">
         <v>0.7</v>
@@ -1591,10 +1591,10 @@
         <v>738</v>
       </c>
       <c r="C56" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D56" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E56">
         <v>0.9</v>
@@ -1608,10 +1608,10 @@
         <v>994</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E57" s="2">
         <v>0.62</v>
@@ -1625,10 +1625,10 @@
         <v>474</v>
       </c>
       <c r="C58" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D58" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E58">
         <v>0.92</v>
@@ -1642,10 +1642,10 @@
         <v>811</v>
       </c>
       <c r="C59" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D59" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E59">
         <v>0.95</v>
@@ -1659,10 +1659,10 @@
         <v>1041</v>
       </c>
       <c r="C60" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D60" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E60">
         <v>0.57856595516204834</v>
@@ -1676,10 +1676,10 @@
         <v>427</v>
       </c>
       <c r="C61" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D61" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E61">
         <v>0.8</v>
@@ -1693,10 +1693,10 @@
         <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D62" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E62">
         <v>0.9</v>
@@ -1710,10 +1710,10 @@
         <v>213</v>
       </c>
       <c r="C63" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D63" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E63">
         <v>0.98</v>
@@ -1727,10 +1727,10 @@
         <v>42</v>
       </c>
       <c r="C64" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D64" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E64">
         <v>1</v>
@@ -1744,10 +1744,10 @@
         <v>240</v>
       </c>
       <c r="C65" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D65" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E65">
         <v>1</v>
@@ -1761,10 +1761,10 @@
         <v>391</v>
       </c>
       <c r="C66" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D66" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E66">
         <v>0.54029422998428345</v>
@@ -1778,10 +1778,10 @@
         <v>811</v>
       </c>
       <c r="C67" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D67" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E67">
         <v>0.77</v>
@@ -1795,10 +1795,10 @@
         <v>44</v>
       </c>
       <c r="C68" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D68" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E68">
         <v>0.78</v>
@@ -1812,10 +1812,10 @@
         <v>895</v>
       </c>
       <c r="C69" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D69" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E69">
         <v>1</v>
@@ -1829,10 +1829,10 @@
         <v>1013</v>
       </c>
       <c r="C70" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D70" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E70">
         <v>0.9</v>
@@ -1846,10 +1846,10 @@
         <v>240</v>
       </c>
       <c r="C71" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D71" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -1863,10 +1863,10 @@
         <v>712</v>
       </c>
       <c r="C72" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D72" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E72">
         <v>0.85</v>
@@ -1880,10 +1880,10 @@
         <v>240</v>
       </c>
       <c r="C73" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D73" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E73">
         <v>1</v>
@@ -1897,10 +1897,10 @@
         <v>470</v>
       </c>
       <c r="C74" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D74" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E74">
         <v>1</v>
@@ -1914,10 +1914,10 @@
         <v>213</v>
       </c>
       <c r="C75" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D75" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E75">
         <v>0.9</v>
@@ -1931,10 +1931,10 @@
         <v>895</v>
       </c>
       <c r="C76" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D76" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E76">
         <v>0.75</v>
@@ -1948,10 +1948,10 @@
         <v>671</v>
       </c>
       <c r="C77" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D77" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E77">
         <v>0.92</v>
@@ -1965,10 +1965,10 @@
         <v>1034</v>
       </c>
       <c r="C78" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D78" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E78">
         <v>0.96</v>
@@ -1982,10 +1982,10 @@
         <v>13</v>
       </c>
       <c r="C79" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D79" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E79">
         <v>0.60661077499389648</v>
@@ -1999,10 +1999,10 @@
         <v>325</v>
       </c>
       <c r="C80" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D80" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E80">
         <v>0.45585787296295172</v>
@@ -2016,10 +2016,10 @@
         <v>304</v>
       </c>
       <c r="C81" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D81" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E81">
         <v>1</v>
@@ -2033,10 +2033,10 @@
         <v>391</v>
       </c>
       <c r="C82" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D82" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E82">
         <v>0.64289402961730957</v>
@@ -2050,10 +2050,10 @@
         <v>740</v>
       </c>
       <c r="C83" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D83" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E83">
         <v>0.62479013204574585</v>
@@ -2067,10 +2067,10 @@
         <v>325</v>
       </c>
       <c r="C84" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D84" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E84">
         <v>0.54179960489273071</v>
@@ -2084,10 +2084,10 @@
         <v>213</v>
       </c>
       <c r="C85" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D85" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E85">
         <v>0.62921535968780518</v>
@@ -2101,10 +2101,10 @@
         <v>231</v>
       </c>
       <c r="C86" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D86" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E86">
         <v>0.60121119022369385</v>
@@ -2118,10 +2118,10 @@
         <v>50</v>
       </c>
       <c r="C87" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D87" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E87">
         <v>0.624839186668396</v>
@@ -2135,10 +2135,10 @@
         <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D88" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E88">
         <v>0.56857538223266602</v>
@@ -2152,10 +2152,10 @@
         <v>231</v>
       </c>
       <c r="C89" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D89" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E89">
         <v>0.60121119022369385</v>
@@ -2169,10 +2169,10 @@
         <v>995</v>
       </c>
       <c r="C90" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D90" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E90">
         <v>0.53529804944992065</v>
@@ -2186,10 +2186,10 @@
         <v>444</v>
       </c>
       <c r="C91" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D91" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E91">
         <v>0.59985661506652832</v>
@@ -2203,10 +2203,10 @@
         <v>391</v>
       </c>
       <c r="C92" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D92" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E92">
         <v>0.56909620761871338</v>
@@ -2220,10 +2220,10 @@
         <v>992</v>
       </c>
       <c r="C93" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D93" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E93">
         <v>0.61768746376037598</v>
@@ -2237,10 +2237,10 @@
         <v>1159</v>
       </c>
       <c r="C94" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D94" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E94">
         <v>0.57880902290344238</v>
@@ -2254,10 +2254,10 @@
         <v>304</v>
       </c>
       <c r="C95" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D95" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E95">
         <v>0.67829585075378418</v>
@@ -2271,10 +2271,10 @@
         <v>240</v>
       </c>
       <c r="C96" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D96" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E96">
         <v>0.50677531957626343</v>
@@ -2288,10 +2288,10 @@
         <v>50</v>
       </c>
       <c r="C97" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D97" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E97">
         <v>0.52854466438293457</v>
@@ -2305,10 +2305,10 @@
         <v>391</v>
       </c>
       <c r="C98" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D98" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E98">
         <v>0.60087299346923828</v>
@@ -2322,10 +2322,10 @@
         <v>12</v>
       </c>
       <c r="C99" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D99" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E99">
         <v>0.59785550832748413</v>
@@ -2339,10 +2339,10 @@
         <v>1018</v>
       </c>
       <c r="C100" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D100" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E100">
         <v>0.62449467182159424</v>
@@ -2356,10 +2356,10 @@
         <v>12</v>
       </c>
       <c r="C101" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D101" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E101">
         <v>0.56807112693786621</v>
